--- a/study_case_model/scenario_variables/other_experiment_data/demand_scenarios133.xlsx
+++ b/study_case_model/scenario_variables/other_experiment_data/demand_scenarios133.xlsx
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>28725.35614758425</v>
+        <v>27765.04981654676</v>
       </c>
     </row>
     <row r="3">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>23963.01774121611</v>
+        <v>22049.95890754479</v>
       </c>
     </row>
     <row r="6">
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>14928.8320178776</v>
+        <v>12607.79308600556</v>
       </c>
     </row>
     <row r="9">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>29138.17913844815</v>
+        <v>27670.7111756438</v>
       </c>
     </row>
     <row r="12">
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7284.544784612039</v>
+        <v>6917.677793910949</v>
       </c>
     </row>
     <row r="14">
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>46487.69937914996</v>
+        <v>52866.48602029855</v>
       </c>
     </row>
     <row r="15">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>11621.98641144057</v>
+        <v>12674.13705558556</v>
       </c>
     </row>
     <row r="18">
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>36844.09611630544</v>
+        <v>14801.07894265061</v>
       </c>
     </row>
     <row r="21">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>30755.76046864681</v>
+        <v>30596.90174520415</v>
       </c>
     </row>
     <row r="24">
@@ -977,7 +977,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>10739.47105274393</v>
+        <v>14920.56567927903</v>
       </c>
     </row>
     <row r="27">
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>23255.36026151579</v>
+        <v>32979.52833983276</v>
       </c>
     </row>
     <row r="30">
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5813.840065378947</v>
+        <v>8244.88208495819</v>
       </c>
     </row>
     <row r="32">
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>43048.73460781306</v>
+        <v>45383.32647570499</v>
       </c>
     </row>
     <row r="33">
@@ -1166,7 +1166,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>10753.51342411154</v>
+        <v>13321.81372873977</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>26814.71703674526</v>
+        <v>26870.37762783067</v>
       </c>
     </row>
     <row r="39">
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>10650.39816506652</v>
+        <v>36830.89959822606</v>
       </c>
     </row>
     <row r="42">
@@ -1355,7 +1355,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6031.558128076127</v>
+        <v>12142.64175354893</v>
       </c>
     </row>
     <row r="45">
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>16626.27482455417</v>
+        <v>21674.12915462203</v>
       </c>
     </row>
     <row r="48">
@@ -1460,7 +1460,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4156.568706138542</v>
+        <v>5418.532288655509</v>
       </c>
     </row>
     <row r="50">
@@ -1481,7 +1481,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>34807.53319498364</v>
+        <v>59118.44764574809</v>
       </c>
     </row>
     <row r="51">
@@ -1544,7 +1544,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>13678.42749723228</v>
+        <v>13199.78421183634</v>
       </c>
     </row>
     <row r="54">

--- a/study_case_model/scenario_variables/other_experiment_data/demand_scenarios133.xlsx
+++ b/study_case_model/scenario_variables/other_experiment_data/demand_scenarios133.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,27 +417,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>stage</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>scenario_index</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>node</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>supplier</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>demand</t>
         </is>
@@ -473,7 +461,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>27765.04981654676</v>
+        <v>25436.565388345</v>
       </c>
     </row>
     <row r="3">
@@ -536,7 +524,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>22049.95890754479</v>
+        <v>16427.72276627033</v>
       </c>
     </row>
     <row r="6">
@@ -599,7 +587,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>12607.79308600556</v>
+        <v>13841.70260130606</v>
       </c>
     </row>
     <row r="9">
@@ -662,7 +650,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>27670.7111756438</v>
+        <v>23364.70715820941</v>
       </c>
     </row>
     <row r="12">
@@ -704,7 +692,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6917.677793910949</v>
+        <v>5841.176789552352</v>
       </c>
     </row>
     <row r="14">
@@ -725,7 +713,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>52866.48602029855</v>
+        <v>66245.76864762916</v>
       </c>
     </row>
     <row r="15">
@@ -788,7 +776,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>12674.13705558556</v>
+        <v>16451.75769513089</v>
       </c>
     </row>
     <row r="18">
@@ -851,7 +839,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>14801.07894265061</v>
+        <v>14667.47974032182</v>
       </c>
     </row>
     <row r="21">
@@ -914,7 +902,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>30596.90174520415</v>
+        <v>17966.31220063658</v>
       </c>
     </row>
     <row r="24">
@@ -977,7 +965,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>14920.56567927903</v>
+        <v>14431.38225203247</v>
       </c>
     </row>
     <row r="27">
@@ -1040,7 +1028,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>32979.52833983276</v>
+        <v>23082.71570547325</v>
       </c>
     </row>
     <row r="30">
@@ -1082,7 +1070,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>8244.88208495819</v>
+        <v>5770.678926368313</v>
       </c>
     </row>
     <row r="32">
@@ -1103,7 +1091,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>45383.32647570499</v>
+        <v>57725.71529459071</v>
       </c>
     </row>
     <row r="33">
@@ -1166,7 +1154,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>13321.81372873977</v>
+        <v>26947.7430899552</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1217,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>26870.37762783067</v>
+        <v>29281.67883019875</v>
       </c>
     </row>
     <row r="39">
@@ -1292,7 +1280,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>36830.89959822606</v>
+        <v>33516.74230135449</v>
       </c>
     </row>
     <row r="42">
@@ -1355,7 +1343,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>12142.64175354893</v>
+        <v>16077.50661309951</v>
       </c>
     </row>
     <row r="45">
@@ -1418,7 +1406,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>21674.12915462203</v>
+        <v>23908.34750783479</v>
       </c>
     </row>
     <row r="48">
@@ -1460,7 +1448,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5418.532288655509</v>
+        <v>5977.086876958698</v>
       </c>
     </row>
     <row r="50">
@@ -1481,7 +1469,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>59118.44764574809</v>
+        <v>45270.96133039481</v>
       </c>
     </row>
     <row r="51">
@@ -1544,7 +1532,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>13199.78421183634</v>
+        <v>15346.13457684975</v>
       </c>
     </row>
     <row r="54">
